--- a/artfynd/A 43883-2024 artfynd.xlsx
+++ b/artfynd/A 43883-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Johan Råghall</t>
+          <t>Johan Råghall, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Johan Råghall</t>
+          <t>Johan Råghall, Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 43883-2024 artfynd.xlsx
+++ b/artfynd/A 43883-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>134380435</v>
       </c>
       <c r="B4" t="n">
-        <v>101291</v>
+        <v>101298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Johan Råghall</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1029,7 +1029,7 @@
         <v>134380444</v>
       </c>
       <c r="B5" t="n">
-        <v>99932</v>
+        <v>99939</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Yasmine Kindlund</t>
+          <t>Yasmine Kindlund, Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 43883-2024 artfynd.xlsx
+++ b/artfynd/A 43883-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61830100</v>
+        <v>94338841</v>
       </c>
       <c r="B2" t="n">
-        <v>97040</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222356</v>
+        <v>502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Frösöstarr</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex pediformis</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>C. A. Mey.</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Frösövallen / S /, Jmt</t>
+          <t>Timmerlada, Stensgårdsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476352.8772087506</v>
+        <v>476447</v>
       </c>
       <c r="R2" t="n">
-        <v>7004762.200783533</v>
+        <v>7004637</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,27 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-05-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Valla 10:25, ca 175 m sydost om Frösövallen. Under träd, tämligen utbredd.</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,21 +757,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -800,12 +776,7 @@
         <v>61830098</v>
       </c>
       <c r="B3" t="n">
-        <v>97040</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476343.7406569754</v>
+        <v>476344</v>
       </c>
       <c r="R3" t="n">
-        <v>7004688.180375502</v>
+        <v>7004688</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,19 +841,9 @@
           <t>2006-05-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-05-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,45 +880,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134380435</v>
+        <v>61830100</v>
       </c>
       <c r="B4" t="n">
-        <v>101298</v>
+        <v>99869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222356</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Frösöstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Carex pediformis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>C. A. Mey.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stensgårdsberget, Jmt</t>
+          <t>Frösövallen / S /, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476341</v>
+        <v>476353</v>
       </c>
       <c r="R4" t="n">
-        <v>7004639</v>
+        <v>7004762</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,22 +945,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:27</t>
+          <t>2006-05-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:27</t>
+          <t>2006-05-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Valla 10:25, ca 175 m sydost om Frösövallen. Under träd, tämligen utbredd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,16 +966,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund, Johan Råghall</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1029,7 +990,7 @@
         <v>134380444</v>
       </c>
       <c r="B5" t="n">
-        <v>99939</v>
+        <v>99946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,6 +1091,220 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120752001</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>MD16:Frösön, Östersund, Sweden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476484</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7004651</v>
+      </c>
+      <c r="S6" t="n">
+        <v>13</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134380435</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stensgårdsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476341</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7004639</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43883-2024 artfynd.xlsx
+++ b/artfynd/A 43883-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,6 +1306,200 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134724824</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stensgårdsberget, Stensgårdsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476322</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7004631</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134725318</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stensgårdsberget, Stensgårdsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>476405</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7004768</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43883-2024 artfynd.xlsx
+++ b/artfynd/A 43883-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94338841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61830098</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61830100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134380444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752001</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134380435</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134724824</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1499,8 +1539,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134725318</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>